--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -484,7 +484,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -555,14 +555,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUN 2026</t>
+BP UPTO JUL 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUN 2026</t>
+Actuals Upto JUL 2026</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -613,36 +613,36 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>160,380
-Cr. 16.04</t>
+          <t>213,841
+Cr. 21.38</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>176,884
-Cr. 17.69</t>
+          <t>232,594
+Cr. 23.26</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>16,504
-Cr. 1.65</t>
+          <t>18,753
+Cr. 1.88</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>110 🔴</t>
+          <t>109 🔴</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>464,638
-Cr. 46.46</t>
+          <t>408,928
+Cr. 40.89</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>28 🟢</t>
+          <t>36 🟢</t>
         </is>
       </c>
     </row>
@@ -665,36 +665,36 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>902,226
-Cr. 90.22</t>
+          <t>1,202,967
+Cr. 120.30</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,105,970
-Cr. 110.60</t>
+          <t>1,467,818
+Cr. 146.78</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>203,744
-Cr. 20.37</t>
+          <t>264,851
+Cr. 26.49</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>123 🔴</t>
+          <t>122 🔴</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>2,502,932
-Cr. 250.29</t>
+          <t>2,141,084
+Cr. 214.11</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>31 🟢</t>
+          <t>41 🟢</t>
         </is>
       </c>
     </row>
@@ -717,36 +717,36 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>466,211
-Cr. 46.62</t>
+          <t>621,614
+Cr. 62.16</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>273,692
-Cr. 27.37</t>
+          <t>782,032
+Cr. 78.20</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>-192,519
-Cr. -19.25</t>
+          <t>160,418
+Cr. 16.04</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>59 🟢</t>
+          <t>126 🔴</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1,591,151
-Cr. 159.12</t>
+          <t>1,082,811
+Cr. 108.28</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>15 🟢</t>
+          <t>42 🟢</t>
         </is>
       </c>
     </row>
@@ -769,36 +769,36 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>338,395
-Cr. 33.84</t>
+          <t>451,194
+Cr. 45.12</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>597,993
-Cr. 59.80</t>
+          <t>722,606
+Cr. 72.26</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>259,598
-Cr. 25.96</t>
+          <t>271,412
+Cr. 27.14</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>177 🔴</t>
+          <t>160 🔴</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>755,588
-Cr. 75.56</t>
+          <t>630,975
+Cr. 63.10</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>44 🟢</t>
+          <t>53 🟢</t>
         </is>
       </c>
     </row>
@@ -821,20 +821,20 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>514,988
-Cr. 51.50</t>
+          <t>686,650
+Cr. 68.67</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>601,809
-Cr. 60.18</t>
+          <t>800,112
+Cr. 80.01</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>86,822
-Cr. 8.68</t>
+          <t>113,462
+Cr. 11.35</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -844,13 +844,13 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,458,141
-Cr. 145.81</t>
+          <t>1,259,838
+Cr. 125.98</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>29 🟢</t>
+          <t>39 🟢</t>
         </is>
       </c>
     </row>
@@ -873,36 +873,36 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>838,142
-Cr. 83.81</t>
+          <t>1,117,522
+Cr. 111.75</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,217,145
-Cr. 121.71</t>
+          <t>1,562,963
+Cr. 156.30</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>379,004
-Cr. 37.90</t>
+          <t>445,441
+Cr. 44.54</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>145 🔴</t>
+          <t>140 🔴</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>2,135,421
-Cr. 213.54</t>
+          <t>1,789,603
+Cr. 178.96</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>36 🟢</t>
+          <t>47 🟢</t>
         </is>
       </c>
     </row>
@@ -925,20 +925,20 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,107,192
-Cr. 110.72</t>
+          <t>1,476,255
+Cr. 147.63</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1,324,129
-Cr. 132.41</t>
+          <t>1,777,301
+Cr. 177.73</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>216,938
-Cr. 21.69</t>
+          <t>301,046
+Cr. 30.10</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -948,13 +948,13 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>3,104,637
-Cr. 310.46</t>
+          <t>2,651,465
+Cr. 265.15</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>30 🟢</t>
+          <t>40 🟢</t>
         </is>
       </c>
     </row>
@@ -977,36 +977,36 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2,901,802
-Cr. 290.18</t>
+          <t>3,869,069
+Cr. 386.91</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3,481,716
-Cr. 348.17</t>
+          <t>3,545,214
+Cr. 354.52</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>579,914
-Cr. 57.99</t>
+          <t>-323,855
+Cr. -32.39</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>120 🔴</t>
+          <t>92 🟠</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8,125,490
-Cr. 812.55</t>
+          <t>8,061,992
+Cr. 806.20</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>30 🟢</t>
+          <t>31 🟢</t>
         </is>
       </c>
     </row>
@@ -1029,36 +1029,36 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>348,208
-Cr. 34.82</t>
+          <t>464,277
+Cr. 46.43</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>670,965
-Cr. 67.10</t>
+          <t>807,750
+Cr. 80.78</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>322,757
-Cr. 32.28</t>
+          <t>343,473
+Cr. 34.35</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>193 🔴</t>
+          <t>174 🔴</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>721,867
-Cr. 72.19</t>
+          <t>585,082
+Cr. 58.51</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>48 🟢</t>
+          <t>58 🟢</t>
         </is>
       </c>
     </row>
@@ -1081,36 +1081,36 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>248,660
-Cr. 24.87</t>
+          <t>331,546
+Cr. 33.15</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>260,994
-Cr. 26.10</t>
+          <t>355,866
+Cr. 35.59</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>12,334
-Cr. 1.23</t>
+          <t>24,320
+Cr. 2.43</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>105 🔴</t>
+          <t>107 🔴</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>733,644
-Cr. 73.36</t>
+          <t>638,772
+Cr. 63.88</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>26 🟢</t>
+          <t>36 🟢</t>
         </is>
       </c>
     </row>
@@ -1133,20 +1133,20 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>322,767
-Cr. 32.28</t>
+          <t>430,356
+Cr. 43.04</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>318,731
-Cr. 31.87</t>
+          <t>425,678
+Cr. 42.57</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>-4,036
-Cr. -0.40</t>
+          <t>-4,678
+Cr. -0.47</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1156,13 +1156,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>972,336
-Cr. 97.23</t>
+          <t>865,389
+Cr. 86.54</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>25 🟢</t>
+          <t>33 🟢</t>
         </is>
       </c>
     </row>
@@ -1181,36 +1181,36 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>8,148,968
-Cr. 814.90</t>
+          <t>10,865,291
+Cr. 1086.53</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>10,030,028
-Cr. 1003.00</t>
+          <t>12,479,934
+Cr. 1247.99</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1,881,060
-Cr. 188.11</t>
+          <t>1,614,643
+Cr. 161.46</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>123 🔴</t>
+          <t>115 🔴</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>22,565,845
-Cr. 2256.58</t>
+          <t>20,115,939
+Cr. 2011.59</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>31 🟢</t>
+          <t>38 🟢</t>
         </is>
       </c>
     </row>
@@ -1233,36 +1233,36 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>-3,261
-Cr. -0.33</t>
+          <t>-4,348
+Cr. -0.43</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,463,486
-Cr. 146.35</t>
+          <t>1,569,032
+Cr. 156.90</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1,466,747
-Cr. 146.67</t>
+          <t>1,573,380
+Cr. 157.34</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-44875 🟢</t>
+          <t>-36084 🟢</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,476,531
-Cr. -147.65</t>
+          <t>-1,582,077
+Cr. -158.21</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-11219 🟢</t>
+          <t>-12028 🟢</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1346,14 +1346,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUN 2026</t>
+BP UPTO JUL 2026</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUN 2026</t>
+Actuals Upto JUL 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1399,36 +1399,36 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1,676,602
-Cr. 167.66</t>
+          <t>2,235,470
+Cr. 223.55</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1,830,978
-Cr. 183.10</t>
+          <t>2,454,892
+Cr. 245.49</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>154,376
-Cr. 15.44</t>
+          <t>219,422
+Cr. 21.94</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>109 🔴</t>
+          <t>110 🔴</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4,875,431
-Cr. 487.54</t>
+          <t>4,251,517
+Cr. 425.15</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>27 🟢</t>
+          <t>37 🟢</t>
         </is>
       </c>
     </row>
@@ -1446,20 +1446,20 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,025,113
-Cr. 102.51</t>
+          <t>1,366,818
+Cr. 136.68</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,188,851
-Cr. 118.89</t>
+          <t>1,579,845
+Cr. 157.98</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>163,738
-Cr. 16.37</t>
+          <t>213,027
+Cr. 21.30</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1469,13 +1469,13 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,911,602
-Cr. 291.16</t>
+          <t>2,520,608
+Cr. 252.06</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>29 🟢</t>
+          <t>39 🟢</t>
         </is>
       </c>
     </row>
@@ -1493,8 +1493,8 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>71,272
-Cr. 7.13</t>
+          <t>95,030
+Cr. 9.50</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1505,8 +1505,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-71,191
-Cr. -7.12</t>
+          <t>-94,949
+Cr. -9.49</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1540,20 +1540,20 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>194,050
-Cr. 19.40</t>
+          <t>258,733
+Cr. 25.87</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>201,303
-Cr. 20.13</t>
+          <t>269,991
+Cr. 27.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>7,254
-Cr. 0.73</t>
+          <t>11,258
+Cr. 1.13</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1563,13 +1563,13 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>574,895
-Cr. 57.49</t>
+          <t>506,207
+Cr. 50.62</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>26 🟢</t>
+          <t>35 🟢</t>
         </is>
       </c>
     </row>
@@ -1587,20 +1587,20 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>124,152
-Cr. 12.42</t>
+          <t>165,536
+Cr. 16.55</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>130,168
-Cr. 13.02</t>
+          <t>173,507
+Cr. 17.35</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6,016
-Cr. 0.60</t>
+          <t>7,971
+Cr. 0.80</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1610,13 +1610,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>366,441
-Cr. 36.64</t>
+          <t>323,102
+Cr. 32.31</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>26 🟢</t>
+          <t>35 🟢</t>
         </is>
       </c>
     </row>
@@ -1634,36 +1634,36 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>170,049
-Cr. 17.00</t>
+          <t>226,732
+Cr. 22.67</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>218,804
-Cr. 21.88</t>
+          <t>290,482
+Cr. 29.05</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>48,755
-Cr. 4.88</t>
+          <t>63,750
+Cr. 6.37</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>129 🔴</t>
+          <t>128 🔴</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>461,393
-Cr. 46.14</t>
+          <t>389,715
+Cr. 38.97</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>32 🟢</t>
+          <t>43 🟢</t>
         </is>
       </c>
     </row>
@@ -1681,36 +1681,36 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>19,325
-Cr. 1.93</t>
+          <t>25,767
+Cr. 2.58</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>43,958
-Cr. 4.40</t>
+          <t>54,545
+Cr. 5.45</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>24,633
-Cr. 2.46</t>
+          <t>28,778
+Cr. 2.88</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>227 🔴</t>
+          <t>212 🔴</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>33,342
-Cr. 3.33</t>
+          <t>22,755
+Cr. 2.28</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>57 🟢</t>
+          <t>71 🟢</t>
         </is>
       </c>
     </row>
@@ -1728,20 +1728,20 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>52,478
-Cr. 5.25</t>
+          <t>69,971
+Cr. 7.00</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>73,688
-Cr. 7.37</t>
+          <t>98,022
+Cr. 9.80</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>21,210
-Cr. 2.12</t>
+          <t>28,051
+Cr. 2.81</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1751,13 +1751,13 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>136,225
-Cr. 13.62</t>
+          <t>111,891
+Cr. 11.19</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>35 🟢</t>
+          <t>47 🟢</t>
         </is>
       </c>
     </row>
@@ -1775,36 +1775,36 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>131,958
-Cr. 13.20</t>
+          <t>175,944
+Cr. 17.59</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>115,964
-Cr. 11.60</t>
+          <t>250,793
+Cr. 25.08</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>-15,994
-Cr. -1.60</t>
+          <t>74,849
+Cr. 7.48</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>88 🟠</t>
+          <t>143 🔴</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>411,868
-Cr. 41.19</t>
+          <t>277,039
+Cr. 27.70</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>22 🟢</t>
+          <t>48 🟢</t>
         </is>
       </c>
     </row>
@@ -1822,36 +1822,36 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>4,012
-Cr. 0.40</t>
+          <t>5,349
+Cr. 0.53</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>5,394
-Cr. 0.54</t>
+          <t>9,177
+Cr. 0.92</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1,382
-Cr. 0.14</t>
+          <t>3,828
+Cr. 0.38</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>134 🔴</t>
+          <t>172 🔴</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>10,654
-Cr. 1.07</t>
+          <t>6,871
+Cr. 0.69</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>34 🟢</t>
+          <t>57 🟢</t>
         </is>
       </c>
     </row>
@@ -1869,36 +1869,36 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>77,020
-Cr. 7.70</t>
+          <t>102,694
+Cr. 10.27</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>130,831
-Cr. 13.08</t>
+          <t>176,120
+Cr. 17.61</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>53,811
-Cr. 5.38</t>
+          <t>73,426
+Cr. 7.34</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>170 🔴</t>
+          <t>172 🔴</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>177,250
-Cr. 17.73</t>
+          <t>131,961
+Cr. 13.20</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>42 🟢</t>
+          <t>57 🟢</t>
         </is>
       </c>
     </row>
@@ -1916,36 +1916,36 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>94,854
-Cr. 9.49</t>
+          <t>126,473
+Cr. 12.65</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>318,899
-Cr. 31.89</t>
+          <t>358,455
+Cr. 35.85</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>224,044
-Cr. 22.40</t>
+          <t>231,982
+Cr. 23.20</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>336 🔴</t>
+          <t>283 🔴</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>60,519
-Cr. 6.05</t>
+          <t>20,963
+Cr. 2.10</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>84 🟠</t>
+          <t>94 🟠</t>
         </is>
       </c>
     </row>
@@ -1963,36 +1963,36 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3,640,887
-Cr. 364.09</t>
+          <t>4,854,516
+Cr. 485.45</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>4,258,919
-Cr. 425.89</t>
+          <t>5,715,910
+Cr. 571.59</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>618,032
-Cr. 61.80</t>
+          <t>861,394
+Cr. 86.14</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>117 🔴</t>
+          <t>118 🔴</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>10,304,628
-Cr. 1030.46</t>
+          <t>8,847,637
+Cr. 884.76</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>29 🟢</t>
+          <t>39 🟢</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -2076,14 +2076,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUN 2026</t>
+BP UPTO JUL 2026</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUN 2026</t>
+Actuals Upto JUL 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2129,31 +2129,31 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>267,188
-Cr. 26.72</t>
+          <t>356,251
+Cr. 35.63</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>588,298
+          <t>588,317
 Cr. 58.83</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>321,110
-Cr. 32.11</t>
+          <t>232,066
+Cr. 23.21</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>220 🔴</t>
+          <t>165 🔴</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>480,454
-Cr. 48.05</t>
+          <t>480,435
+Cr. 48.04</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2176,36 +2176,36 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>37,487
-Cr. 3.75</t>
+          <t>49,982
+Cr. 5.00</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>42,862
-Cr. 4.29</t>
+          <t>63,019
+Cr. 6.30</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>5,375
-Cr. 0.54</t>
+          <t>13,037
+Cr. 1.30</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>114 🔴</t>
+          <t>126 🔴</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>107,085
-Cr. 10.71</t>
+          <t>86,928
+Cr. 8.69</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>29 🟢</t>
+          <t>42 🟢</t>
         </is>
       </c>
     </row>
@@ -2223,36 +2223,36 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>969,681
-Cr. 96.97</t>
+          <t>1,292,908
+Cr. 129.29</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,014,183
-Cr. 101.42</t>
+          <t>1,100,220
+Cr. 110.02</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>44,502
-Cr. 4.45</t>
+          <t>-192,688
+Cr. -19.27</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>105 🔴</t>
+          <t>85 🟠</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2,864,541
-Cr. 286.45</t>
+          <t>2,778,504
+Cr. 277.85</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>26 🟢</t>
+          <t>28 🟢</t>
         </is>
       </c>
     </row>
@@ -2270,36 +2270,36 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>813,578
-Cr. 81.36</t>
+          <t>1,084,770
+Cr. 108.48</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>966,861
-Cr. 96.69</t>
+          <t>1,658,467
+Cr. 165.85</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>153,284
-Cr. 15.33</t>
+          <t>573,697
+Cr. 57.37</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>119 🔴</t>
+          <t>153 🔴</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>2,287,449
-Cr. 228.74</t>
+          <t>1,595,843
+Cr. 159.58</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>30 🟢</t>
+          <t>51 🟢</t>
         </is>
       </c>
     </row>
@@ -2317,8 +2317,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1,175,839
-Cr. 117.58</t>
+          <t>1,567,785
+Cr. 156.78</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2329,13 +2329,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>631,235
-Cr. 63.12</t>
+          <t>239,289
+Cr. 23.93</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>154 🔴</t>
+          <t>115 🔴</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2364,36 +2364,36 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>3,263,772
-Cr. 326.38</t>
+          <t>4,351,696
+Cr. 435.17</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>4,419,278
-Cr. 441.93</t>
+          <t>5,217,097
+Cr. 521.71</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,155,506
-Cr. 115.55</t>
+          <t>865,401
+Cr. 86.54</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>135 🔴</t>
+          <t>120 🔴</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>8,635,811
-Cr. 863.58</t>
+          <t>7,837,992
+Cr. 783.80</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>34 🟢</t>
+          <t>40 🟢</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2503,19 +2503,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>26,747
-Cr. 2.67</t>
+          <t>49,143
+Cr. 4.91</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-134,156
-Cr. -13.42</t>
+          <t>-111,760
+Cr. -11.18</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>30.54</t>
         </is>
       </c>
     </row>
@@ -2538,19 +2538,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>3,375
-Cr. 0.34</t>
+          <t>3,682
+Cr. 0.37</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-28,852
-Cr. -2.89</t>
+          <t>-28,545
+Cr. -2.85</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>11.43</t>
         </is>
       </c>
     </row>
@@ -2573,19 +2573,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>45,115
-Cr. 4.51</t>
+          <t>49,669
+Cr. 4.97</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-75,203
-Cr. -7.52</t>
+          <t>-70,649
+Cr. -7.06</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>41.28</t>
         </is>
       </c>
     </row>
@@ -2608,19 +2608,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>280,081
-Cr. 28.01</t>
+          <t>314,675
+Cr. 31.47</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-227,339
-Cr. -22.73</t>
+          <t>-192,745
+Cr. -19.27</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>55.20</t>
+          <t>62.01</t>
         </is>
       </c>
     </row>
@@ -2643,19 +2643,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2,309,920
-Cr. 230.99</t>
+          <t>2,356,170
+Cr. 235.62</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-652,875
-Cr. -65.29</t>
+          <t>-606,625
+Cr. -60.66</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>77.96</t>
+          <t>79.53</t>
         </is>
       </c>
     </row>
@@ -2678,19 +2678,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>117,471
-Cr. 11.75</t>
+          <t>135,953
+Cr. 13.60</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-14,796
-Cr. -1.48</t>
+          <t>3,686
+Cr. 0.37</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>102.79</t>
         </is>
       </c>
     </row>
@@ -2713,19 +2713,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>83,786
-Cr. 8.38</t>
+          <t>117,673
+Cr. 11.77</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-439,057
-Cr. -43.91</t>
+          <t>-405,170
+Cr. -40.52</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>22.51</t>
         </is>
       </c>
     </row>
@@ -2748,19 +2748,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>77,718
-Cr. 7.77</t>
+          <t>82,362
+Cr. 8.24</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-230,125
-Cr. -23.01</t>
+          <t>-225,481
+Cr. -22.55</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>26.75</t>
         </is>
       </c>
     </row>
@@ -2818,19 +2818,19 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1,919
-Cr. 0.19</t>
+          <t>3,629
+Cr. 0.36</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-11,275
-Cr. -1.13</t>
+          <t>-9,565
+Cr. -0.96</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>27.50</t>
         </is>
       </c>
     </row>
@@ -2853,13 +2853,13 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2,426
+          <t>2,427
 Cr. 0.24</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-51,276
+          <t>-51,275
 Cr. -5.13</t>
         </is>
       </c>
@@ -2888,19 +2888,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22,047
-Cr. 2.20</t>
+          <t>35,140
+Cr. 3.51</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-75,453
-Cr. -7.55</t>
+          <t>-62,360
+Cr. -6.24</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>36.04</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2923,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>125,504
-Cr. 12.55</t>
+          <t>115,054
+Cr. 11.51</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-185,408
-Cr. -18.54</t>
+          <t>-195,858
+Cr. -19.59</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>37.01</t>
         </is>
       </c>
     </row>
@@ -2993,19 +2993,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>71,352
-Cr. 7.14</t>
+          <t>74,839
+Cr. 7.48</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-244,381
-Cr. -24.44</t>
+          <t>-240,894
+Cr. -24.09</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>22.60</t>
+          <t>23.70</t>
         </is>
       </c>
     </row>
@@ -3085,28 +3085,98 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1. Sr. DEN (C )</t>
+        </is>
+      </c>
       <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2. Sr. DEE (G &amp; TRD)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>5,607,701
 Cr. 560.77</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>3,167,461
-Cr. 316.75</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>-2,440,240
-Cr. -244.02</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>56.48</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>3,340,416
+Cr. 334.04</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>-2,267,285
+Cr. -226.73</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>59.57</t>
         </is>
       </c>
     </row>
@@ -3211,24 +3281,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>262,411
-Cr. 26.24</t>
+          <t>296,990
+Cr. 29.70</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>755,942
-Cr. 75.59</t>
+          <t>721,363
+Cr. 72.14</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>74.23</t>
+          <t>70.84</t>
         </is>
       </c>
     </row>
@@ -3281,24 +3351,24 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>8,107
-Cr. 0.81</t>
+          <t>8,703
+Cr. 0.87</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>122,485
-Cr. 12.25</t>
+          <t>121,889
+Cr. 12.19</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>93.79</t>
+          <t>93.34</t>
         </is>
       </c>
     </row>
@@ -3351,24 +3421,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2,386,001
-Cr. 238.60</t>
+          <t>2,463,326
+Cr. 246.33</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>731,514
-Cr. 73.15</t>
+          <t>654,189
+Cr. 65.42</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>76.54</t>
+          <t>79.02</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>20.98</t>
         </is>
       </c>
     </row>
@@ -3421,24 +3491,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>498,296
-Cr. 49.83</t>
+          <t>558,751
+Cr. 55.88</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>802,713
-Cr. 80.27</t>
+          <t>742,258
+Cr. 74.23</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>38.30</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>57.05</t>
         </is>
       </c>
     </row>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -2409,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2538,19 +2538,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>3,682
-Cr. 0.37</t>
+          <t>5,289
+Cr. 0.53</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-28,545
-Cr. -2.85</t>
+          <t>-26,938
+Cr. -2.69</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>16.41</t>
         </is>
       </c>
     </row>
@@ -2608,19 +2608,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>314,675
-Cr. 31.47</t>
+          <t>320,276
+Cr. 32.03</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-192,745
-Cr. -19.27</t>
+          <t>-187,144
+Cr. -18.71</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>62.01</t>
+          <t>63.12</t>
         </is>
       </c>
     </row>
@@ -2643,19 +2643,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2,356,170
-Cr. 235.62</t>
+          <t>3,020,618
+Cr. 302.06</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-606,625
-Cr. -60.66</t>
+          <t>57,823
+Cr. 5.78</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>79.53</t>
+          <t>101.95</t>
         </is>
       </c>
     </row>
@@ -2713,14 +2713,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>117,673
+          <t>117,717
 Cr. 11.77</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-405,170
-Cr. -40.52</t>
+          <t>-405,126
+Cr. -40.51</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2748,19 +2748,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>82,362
-Cr. 8.24</t>
+          <t>84,759
+Cr. 8.48</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-225,481
-Cr. -22.55</t>
+          <t>-223,084
+Cr. -22.31</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>27.53</t>
         </is>
       </c>
     </row>
@@ -2853,19 +2853,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2,427
-Cr. 0.24</t>
+          <t>4,327
+Cr. 0.43</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-51,275
-Cr. -5.13</t>
+          <t>-49,375
+Cr. -4.94</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2923,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>115,054
-Cr. 11.51</t>
+          <t>116,587
+Cr. 11.66</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-195,858
-Cr. -19.59</t>
+          <t>-194,325
+Cr. -19.43</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>37.50</t>
         </is>
       </c>
     </row>
@@ -2993,19 +2993,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>74,839
-Cr. 7.48</t>
+          <t>80,509
+Cr. 8.05</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-240,894
-Cr. -24.09</t>
+          <t>-235,224
+Cr. -23.52</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>23.70</t>
+          <t>25.50</t>
         </is>
       </c>
     </row>
@@ -3085,98 +3085,28 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>1. Sr. DEN (C )</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>2. Sr. DEE (G &amp; TRD)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>5,607,701
 Cr. 560.77</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>3,340,416
-Cr. 334.04</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>-2,267,285
-Cr. -226.73</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>59.57</t>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>4,023,616
+Cr. 402.36</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>-1,584,085
+Cr. -158.41</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>71.75</t>
         </is>
       </c>
     </row>
@@ -3281,24 +3211,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>296,990
-Cr. 29.70</t>
+          <t>301,883
+Cr. 30.19</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>721,363
-Cr. 72.14</t>
+          <t>716,470
+Cr. 71.65</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>70.84</t>
+          <t>70.36</t>
         </is>
       </c>
     </row>
@@ -3316,24 +3246,24 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>12,646
-Cr. 1.26</t>
+          <t>14,031
+Cr. 1.40</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>27,586
-Cr. 2.76</t>
+          <t>26,201
+Cr. 2.62</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>65.12</t>
         </is>
       </c>
     </row>
@@ -3351,24 +3281,24 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>8,703
-Cr. 0.87</t>
+          <t>10,251
+Cr. 1.03</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>121,889
-Cr. 12.19</t>
+          <t>120,341
+Cr. 12.03</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>93.34</t>
+          <t>92.15</t>
         </is>
       </c>
     </row>
@@ -3421,24 +3351,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2,463,326
-Cr. 246.33</t>
+          <t>3,103,250
+Cr. 310.32</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>654,189
-Cr. 65.42</t>
+          <t>14,265
+Cr. 1.43</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>79.02</t>
+          <t>99.54</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>0.46</t>
         </is>
       </c>
     </row>
@@ -3491,24 +3421,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>558,751
-Cr. 55.88</t>
+          <t>594,201
+Cr. 59.42</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>742,258
-Cr. 74.23</t>
+          <t>706,808
+Cr. 70.68</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>57.05</t>
+          <t>54.33</t>
         </is>
       </c>
     </row>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -487,9 +487,9 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>109 🔴</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>36 🟢</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>122 🔴</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>41 🟢</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>126 🔴</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>42 🟢</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>160 🔴</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>53 🟢</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>117 🔴</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>39 🟢</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>140 🔴</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>47 🟢</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>120 🔴</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>40 🟢</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>92 🟠</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>31 🟢</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>174 🔴</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>58 🟢</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>107 🔴</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>36 🟢</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>99 🟠</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>33 🟢</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>115 🔴</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>38 🟢</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-36084 🟢</t>
+          <t>-36084</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12028 🟢</t>
+          <t>-12028</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>110 🔴</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>37 🟢</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>116 🔴</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>39 🟢</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0 🟢</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>0 🟢</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>104 🔴</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>35 🟢</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105 🔴</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>35 🟢</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>128 🔴</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>43 🟢</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>212 🔴</t>
+          <t>212</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>71 🟢</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>140 🔴</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>47 🟢</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>143 🔴</t>
+          <t>143</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>48 🟢</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>172 🔴</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>57 🟢</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>172 🔴</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>57 🟢</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>283 🔴</t>
+          <t>283</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>94 🟠</t>
+          <t>94</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>118 🔴</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>39 🟢</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>165 🔴</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>55 🟢</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>126 🔴</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>42 🟢</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>85 🟠</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>28 🟢</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>153 🔴</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>51 🟢</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>115 🔴</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>38 🟢</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>120 🔴</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>40 🟢</t>
+          <t>40</t>
         </is>
       </c>
     </row>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -613,8 +613,8 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>213,841
-Cr. 21.38</t>
+          <t>240,031
+Cr. 24.00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -625,13 +625,13 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>18,753
-Cr. 1.88</t>
+          <t>-7,437
+Cr. -0.74</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -665,8 +665,8 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,202,967
-Cr. 120.30</t>
+          <t>1,177,984
+Cr. 117.80</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -677,13 +677,13 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>264,851
-Cr. 26.49</t>
+          <t>289,834
+Cr. 28.98</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -717,8 +717,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>621,614
-Cr. 62.16</t>
+          <t>923,741
+Cr. 92.37</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -729,13 +729,13 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>160,418
-Cr. 16.04</t>
+          <t>-141,709
+Cr. -14.17</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -769,8 +769,8 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>451,194
-Cr. 45.12</t>
+          <t>413,960
+Cr. 41.40</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>271,412
-Cr. 27.14</t>
+          <t>308,646
+Cr. 30.86</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -821,8 +821,8 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>686,650
-Cr. 68.67</t>
+          <t>694,140
+Cr. 69.41</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -833,13 +833,13 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>113,462
-Cr. 11.35</t>
+          <t>105,972
+Cr. 10.60</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -873,8 +873,8 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1,117,522
-Cr. 111.75</t>
+          <t>1,217,272
+Cr. 121.73</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -885,13 +885,13 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>445,441
-Cr. 44.54</t>
+          <t>345,691
+Cr. 34.57</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -925,8 +925,8 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,476,255
-Cr. 147.63</t>
+          <t>1,511,191
+Cr. 151.12</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -937,13 +937,13 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>301,046
-Cr. 30.10</t>
+          <t>266,110
+Cr. 26.61</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -977,8 +977,8 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>3,869,069
-Cr. 386.91</t>
+          <t>3,862,305
+Cr. 386.23</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -989,8 +989,8 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>-323,855
-Cr. -32.39</t>
+          <t>-317,091
+Cr. -31.71</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1029,8 +1029,8 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>464,277
-Cr. 46.43</t>
+          <t>598,674
+Cr. 59.87</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1041,13 +1041,13 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>343,473
-Cr. 34.35</t>
+          <t>209,076
+Cr. 20.91</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1081,8 +1081,8 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>331,546
-Cr. 33.15</t>
+          <t>325,688
+Cr. 32.57</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1093,13 +1093,13 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>24,320
-Cr. 2.43</t>
+          <t>30,178
+Cr. 3.02</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1133,8 +1133,8 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>430,356
-Cr. 43.04</t>
+          <t>388,570
+Cr. 38.86</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1145,13 +1145,13 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>-4,678
-Cr. -0.47</t>
+          <t>37,108
+Cr. 3.71</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1181,8 +1181,8 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>10,865,291
-Cr. 1086.53</t>
+          <t>11,353,556
+Cr. 1135.36</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1193,13 +1193,13 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1,614,643
-Cr. 161.46</t>
+          <t>1,126,378
+Cr. 112.64</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1233,8 +1233,8 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>-4,348
-Cr. -0.43</t>
+          <t>1,362,799
+Cr. 136.28</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1245,13 +1245,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1,573,380
-Cr. 157.34</t>
+          <t>206,233
+Cr. 20.62</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-36084</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1399,8 +1399,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,235,470
-Cr. 223.55</t>
+          <t>2,249,064
+Cr. 224.91</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1411,13 +1411,13 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>219,422
-Cr. 21.94</t>
+          <t>205,828
+Cr. 20.58</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1446,8 +1446,8 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,366,818
-Cr. 136.68</t>
+          <t>1,359,404
+Cr. 135.94</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1458,8 +1458,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>213,027
-Cr. 21.30</t>
+          <t>220,441
+Cr. 22.04</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1493,8 +1493,8 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>95,030
-Cr. 9.50</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1505,8 +1505,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-94,949
-Cr. -9.49</t>
+          <t>81
+Cr. 0.01</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1540,8 +1540,8 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>258,733
-Cr. 25.87</t>
+          <t>268,852
+Cr. 26.89</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1552,13 +1552,13 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>11,258
-Cr. 1.13</t>
+          <t>1,139
+Cr. 0.11</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1587,8 +1587,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>165,536
-Cr. 16.55</t>
+          <t>167,312
+Cr. 16.73</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1599,13 +1599,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>7,971
-Cr. 0.80</t>
+          <t>6,195
+Cr. 0.62</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1634,8 +1634,8 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>226,732
-Cr. 22.67</t>
+          <t>255,207
+Cr. 25.52</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1646,13 +1646,13 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>63,750
-Cr. 6.37</t>
+          <t>35,275
+Cr. 3.53</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1681,8 +1681,8 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>25,767
-Cr. 2.58</t>
+          <t>26,924
+Cr. 2.69</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1693,13 +1693,13 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>28,778
-Cr. 2.88</t>
+          <t>27,621
+Cr. 2.76</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1728,8 +1728,8 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>69,971
-Cr. 7.00</t>
+          <t>69,543
+Cr. 6.95</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1740,13 +1740,13 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>28,051
-Cr. 2.81</t>
+          <t>28,479
+Cr. 2.85</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1775,8 +1775,8 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>175,944
-Cr. 17.59</t>
+          <t>273,477
+Cr. 27.35</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1787,13 +1787,13 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>74,849
-Cr. 7.48</t>
+          <t>-22,684
+Cr. -2.27</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1822,8 +1822,8 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>5,349
-Cr. 0.53</t>
+          <t>5,665
+Cr. 0.57</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1834,13 +1834,13 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>3,828
-Cr. 0.38</t>
+          <t>3,512
+Cr. 0.35</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>162</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1869,8 +1869,8 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102,694
-Cr. 10.27</t>
+          <t>100,083
+Cr. 10.01</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1881,13 +1881,13 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>73,426
-Cr. 7.34</t>
+          <t>76,037
+Cr. 7.60</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1916,8 +1916,8 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>126,473
-Cr. 12.65</t>
+          <t>320,448
+Cr. 32.04</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1928,13 +1928,13 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>231,982
-Cr. 23.20</t>
+          <t>38,007
+Cr. 3.80</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1963,8 +1963,8 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>4,854,516
-Cr. 485.45</t>
+          <t>5,095,979
+Cr. 509.60</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1975,13 +1975,13 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>861,394
-Cr. 86.14</t>
+          <t>619,931
+Cr. 61.99</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2129,8 +2129,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>356,251
-Cr. 35.63</t>
+          <t>350,722
+Cr. 35.07</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2141,13 +2141,13 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>232,066
-Cr. 23.21</t>
+          <t>237,595
+Cr. 23.76</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2176,8 +2176,8 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>49,982
-Cr. 5.00</t>
+          <t>52,719
+Cr. 5.27</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2188,13 +2188,13 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>13,037
-Cr. 1.30</t>
+          <t>10,300
+Cr. 1.03</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2223,8 +2223,8 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1,292,908
-Cr. 129.29</t>
+          <t>1,330,274
+Cr. 133.03</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2235,13 +2235,13 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-192,688
-Cr. -19.27</t>
+          <t>-230,054
+Cr. -23.01</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2270,8 +2270,8 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1,084,770
-Cr. 108.48</t>
+          <t>1,396,328
+Cr. 139.63</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2282,13 +2282,13 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>573,697
-Cr. 57.37</t>
+          <t>262,139
+Cr. 26.21</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2317,8 +2317,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1,567,785
-Cr. 156.78</t>
+          <t>1,538,432
+Cr. 153.84</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2329,13 +2329,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>239,289
-Cr. 23.93</t>
+          <t>268,642
+Cr. 26.86</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2364,8 +2364,8 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4,351,696
-Cr. 435.17</t>
+          <t>4,668,475
+Cr. 466.85</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2376,13 +2376,13 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>865,401
-Cr. 86.54</t>
+          <t>548,622
+Cr. 54.86</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - JUL 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - JUL 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - JU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise</t>
+          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff</t>
+          <t>PU Wise - Staff - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2024,7 +2024,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1</t>
+          <t>PU Wise - Non-Staff Part 1 - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2423,7 +2423,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report</t>
+          <t>Open Line FR Report - As On 17.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2503,19 +2503,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>49,143
-Cr. 4.91</t>
+          <t>77,164
+Cr. 7.72</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-111,760
-Cr. -11.18</t>
+          <t>-83,739
+Cr. -8.37</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>47.96</t>
         </is>
       </c>
     </row>
@@ -2538,19 +2538,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>5,289
-Cr. 0.53</t>
+          <t>8,452
+Cr. 0.85</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-26,938
-Cr. -2.69</t>
+          <t>-23,775
+Cr. -2.38</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>26.23</t>
         </is>
       </c>
     </row>
@@ -2573,19 +2573,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>49,669
-Cr. 4.97</t>
+          <t>55,924
+Cr. 5.59</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-70,649
-Cr. -7.06</t>
+          <t>-64,394
+Cr. -6.44</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>46.48</t>
         </is>
       </c>
     </row>
@@ -2608,19 +2608,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>320,276
-Cr. 32.03</t>
+          <t>327,869
+Cr. 32.79</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-187,144
-Cr. -18.71</t>
+          <t>-179,551
+Cr. -17.96</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>64.61</t>
         </is>
       </c>
     </row>
@@ -2643,19 +2643,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,020,618
-Cr. 302.06</t>
+          <t>3,070,343
+Cr. 307.03</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>57,823
-Cr. 5.78</t>
+          <t>107,548
+Cr. 10.75</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>101.95</t>
+          <t>103.63</t>
         </is>
       </c>
     </row>
@@ -2678,19 +2678,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>135,953
-Cr. 13.60</t>
+          <t>142,510
+Cr. 14.25</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>3,686
-Cr. 0.37</t>
+          <t>10,243
+Cr. 1.02</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>107.74</t>
         </is>
       </c>
     </row>
@@ -2713,19 +2713,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>117,717
-Cr. 11.77</t>
+          <t>120,694
+Cr. 12.07</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-405,126
-Cr. -40.51</t>
+          <t>-402,149
+Cr. -40.21</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>23.08</t>
         </is>
       </c>
     </row>
@@ -2748,19 +2748,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>84,759
-Cr. 8.48</t>
+          <t>92,648
+Cr. 9.26</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-223,084
-Cr. -22.31</t>
+          <t>-215,195
+Cr. -21.52</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>30.10</t>
         </is>
       </c>
     </row>
@@ -2818,19 +2818,19 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>3,629
-Cr. 0.36</t>
+          <t>10,501
+Cr. 1.05</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-9,565
-Cr. -0.96</t>
+          <t>-2,693
+Cr. -0.27</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>79.59</t>
         </is>
       </c>
     </row>
@@ -2888,19 +2888,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>35,140
-Cr. 3.51</t>
+          <t>42,044
+Cr. 4.20</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-62,360
-Cr. -6.24</t>
+          <t>-55,456
+Cr. -5.55</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>43.12</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2923,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>116,587
-Cr. 11.66</t>
+          <t>117,954
+Cr. 11.80</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-194,325
-Cr. -19.43</t>
+          <t>-192,958
+Cr. -19.30</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>37.94</t>
         </is>
       </c>
     </row>
@@ -2993,19 +2993,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>80,509
-Cr. 8.05</t>
+          <t>85,279
+Cr. 8.53</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-235,224
-Cr. -23.52</t>
+          <t>-230,454
+Cr. -23.05</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>25.50</t>
+          <t>27.01</t>
         </is>
       </c>
     </row>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,023,616
-Cr. 402.36</t>
+          <t>4,155,709
+Cr. 415.57</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-1,584,085
-Cr. -158.41</t>
+          <t>-1,451,992
+Cr. -145.20</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>74.11</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise</t>
+          <t>Open Line FR Fund Wise - As On 17.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3211,24 +3211,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>301,883
-Cr. 30.19</t>
+          <t>354,585
+Cr. 35.46</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>716,470
-Cr. 71.65</t>
+          <t>663,768
+Cr. 66.38</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>65.18</t>
         </is>
       </c>
     </row>
@@ -3246,24 +3246,24 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>14,031
-Cr. 1.40</t>
+          <t>15,491
+Cr. 1.55</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>26,201
-Cr. 2.62</t>
+          <t>24,741
+Cr. 2.47</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>38.50</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>61.50</t>
         </is>
       </c>
     </row>
@@ -3281,24 +3281,24 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>10,251
-Cr. 1.03</t>
+          <t>11,290
+Cr. 1.13</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>120,341
-Cr. 12.03</t>
+          <t>119,302
+Cr. 11.93</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>91.35</t>
         </is>
       </c>
     </row>
@@ -3351,24 +3351,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,103,250
-Cr. 310.32</t>
+          <t>3,142,858
+Cr. 314.29</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>14,265
-Cr. 1.43</t>
+          <t>-25,343
+Cr. -2.53</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>99.54</t>
+          <t>100.81</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.81</t>
         </is>
       </c>
     </row>
@@ -3421,24 +3421,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>594,201
-Cr. 59.42</t>
+          <t>631,485
+Cr. 63.15</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>706,808
-Cr. 70.68</t>
+          <t>669,524
+Cr. 66.95</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>48.54</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>51.46</t>
         </is>
       </c>
     </row>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -490,6 +490,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,6 +507,7 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -521,6 +523,7 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -532,6 +535,7 @@
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -593,6 +597,13 @@
 C / A</t>
         </is>
       </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>H
+Actual Final Expenditure
+FY 2025-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -645,6 +656,12 @@
           <t>36</t>
         </is>
       </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>693,876
+Cr. 69.39</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -697,6 +714,12 @@
           <t>41</t>
         </is>
       </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>3,996,057
+Cr. 399.61</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -749,6 +772,12 @@
           <t>42</t>
         </is>
       </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2,000,064
+Cr. 200.01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -801,6 +830,12 @@
           <t>53</t>
         </is>
       </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>1,511,638
+Cr. 151.16</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -853,6 +888,12 @@
           <t>39</t>
         </is>
       </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2,171,600
+Cr. 217.16</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -905,6 +946,12 @@
           <t>47</t>
         </is>
       </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>3,801,767
+Cr. 380.18</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -957,6 +1004,12 @@
           <t>40</t>
         </is>
       </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>4,947,572
+Cr. 494.76</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1009,6 +1062,12 @@
           <t>31</t>
         </is>
       </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>12,690,658
+Cr. 1269.07</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1061,6 +1120,12 @@
           <t>58</t>
         </is>
       </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>1,451,556
+Cr. 145.16</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1113,6 +1178,12 @@
           <t>36</t>
         </is>
       </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>1,025,571
+Cr. 102.56</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1165,6 +1236,12 @@
           <t>33</t>
         </is>
       </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>1,226,809
+Cr. 122.68</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1213,6 +1290,12 @@
           <t>38</t>
         </is>
       </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>35,517,168
+Cr. 3551.72</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1263,6 +1346,12 @@
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>-12028</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>-2,031
+Cr. -0.20</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1289,6 +1378,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1304,6 +1394,7 @@
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1409,7 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -1328,6 +1420,7 @@
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1384,6 +1477,13 @@
 C / A</t>
         </is>
       </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>H
+Actual Final Expenditure
+FY 2025-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1431,6 +1531,12 @@
           <t>37</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>7,351,228
+Cr. 735.12</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1478,6 +1584,12 @@
           <t>39</t>
         </is>
       </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>4,447,868
+Cr. 444.79</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1525,6 +1637,12 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>302,570
+Cr. 30.26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1572,6 +1690,12 @@
           <t>35</t>
         </is>
       </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>802,369
+Cr. 80.24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1619,6 +1743,12 @@
           <t>35</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>509,846
+Cr. 50.98</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1666,6 +1796,12 @@
           <t>43</t>
         </is>
       </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>764,171
+Cr. 76.42</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1713,6 +1849,12 @@
           <t>71</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>106,223
+Cr. 10.62</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1760,6 +1902,12 @@
           <t>47</t>
         </is>
       </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>294,342
+Cr. 29.43</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1807,6 +1955,12 @@
           <t>48</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>519,754
+Cr. 51.98</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1854,6 +2008,12 @@
           <t>57</t>
         </is>
       </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>20,171
+Cr. 2.02</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1901,6 +2061,12 @@
           <t>57</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>523,752
+Cr. 52.38</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1948,6 +2114,12 @@
           <t>94</t>
         </is>
       </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>374,596
+Cr. 37.46</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1993,6 +2165,12 @@
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>39</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>16,016,890
+Cr. 1601.69</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2019,6 +2197,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2034,6 +2213,7 @@
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2048,6 +2228,7 @@
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -2058,6 +2239,7 @@
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2114,6 +2296,13 @@
 C / A</t>
         </is>
       </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>H
+Actual Final Expenditure
+FY 2025-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2161,6 +2350,12 @@
           <t>55</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>1,291,487
+Cr. 129.15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2208,6 +2403,12 @@
           <t>42</t>
         </is>
       </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>164,506
+Cr. 16.45</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2255,6 +2456,12 @@
           <t>28</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>4,115,874
+Cr. 411.59</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2302,6 +2509,12 @@
           <t>51</t>
         </is>
       </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>3,623,756
+Cr. 362.38</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2349,6 +2562,12 @@
           <t>38</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>5,106,358
+Cr. 510.64</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2394,6 +2613,12 @@
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>40</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>14,301,981
+Cr. 1430.20</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2418,6 +2643,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2431,6 +2657,7 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2443,6 +2670,7 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -2451,6 +2679,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2483,6 +2712,13 @@
           <t>% SBA</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>H
+Actual Final Expense
+FY 2025-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2518,6 +2754,11 @@
           <t>47.96</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>4.27 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2553,6 +2794,11 @@
           <t>26.23</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>3.08 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2588,6 +2834,11 @@
           <t>46.48</t>
         </is>
       </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>13.77 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2623,6 +2874,11 @@
           <t>64.61</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>38.44 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2658,6 +2914,11 @@
           <t>103.63</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>613.14 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2693,6 +2954,11 @@
           <t>107.74</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>13.45 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2728,6 +2994,11 @@
           <t>23.08</t>
         </is>
       </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>28.50 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2763,6 +3034,11 @@
           <t>30.10</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>12.47 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2798,6 +3074,11 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>0.00 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2833,6 +3114,11 @@
           <t>79.59</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2.37 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2868,6 +3154,11 @@
           <t>8.06</t>
         </is>
       </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>2.74 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2903,6 +3194,11 @@
           <t>43.12</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>6.85 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2938,6 +3234,11 @@
           <t>37.94</t>
         </is>
       </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>18.48 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2973,6 +3274,11 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>0.00 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3008,6 +3314,11 @@
           <t>27.01</t>
         </is>
       </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>14.30 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3043,6 +3354,11 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>771.97 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -3078,6 +3394,11 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>0.11 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3107,6 +3428,11 @@
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>74.11</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>771.97 Cr</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3131,6 +3457,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3144,6 +3471,7 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3156,6 +3484,7 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -3164,6 +3493,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3196,6 +3526,13 @@
           <t>Remaining %</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>H
+Actual Final Expense
+FY 2025-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3231,6 +3568,11 @@
           <t>65.18</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>46.39 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -3266,6 +3608,11 @@
           <t>61.50</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>5.12 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3301,6 +3648,11 @@
           <t>91.35</t>
         </is>
       </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>4.52 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -3336,6 +3688,11 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>0.00 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3371,6 +3728,11 @@
           <t>-0.81</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>617.23 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3406,6 +3768,11 @@
           <t>0.00</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>0.00 Cr</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3439,6 +3806,11 @@
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>51.46</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>98.70 Cr</t>
         </is>
       </c>
     </row>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -3321,11 +3321,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="5" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>OSW (CAPIN)</t>
@@ -3356,7 +3352,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>771.97 Cr</t>
+          <t>0.00 Cr</t>
         </is>
       </c>
     </row>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1384,7 +1384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>PU Wise - Staff - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2203,7 +2203,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - JUL 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - JUL 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - JU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 27." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -2649,7 +2649,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 17.08.2026</t>
+          <t>Open Line FR Report - As On 27.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2739,13 +2739,13 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,164
+          <t>77,175
 Cr. 7.72</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-83,739
+          <t>-83,728
 Cr. -8.37</t>
         </is>
       </c>
@@ -2779,19 +2779,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>8,452
-Cr. 0.85</t>
+          <t>10,761
+Cr. 1.08</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-23,775
-Cr. -2.38</t>
+          <t>-21,466
+Cr. -2.15</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>55,924
-Cr. 5.59</t>
+          <t>57,023
+Cr. 5.70</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-64,394
-Cr. -6.44</t>
+          <t>-63,295
+Cr. -6.33</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2859,19 +2859,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>327,869
-Cr. 32.79</t>
+          <t>337,625
+Cr. 33.76</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-179,551
-Cr. -17.96</t>
+          <t>-169,795
+Cr. -16.98</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2899,19 +2899,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,070,343
-Cr. 307.03</t>
+          <t>3,110,796
+Cr. 311.08</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>107,548
-Cr. 10.75</t>
+          <t>148,001
+Cr. 14.80</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>103.63</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>142,510
-Cr. 14.25</t>
+          <t>150,620
+Cr. 15.06</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>10,243
-Cr. 1.02</t>
+          <t>18,353
+Cr. 1.84</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>107.74</t>
+          <t>113.88</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2979,19 +2979,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>120,694
-Cr. 12.07</t>
+          <t>120,775
+Cr. 12.08</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-402,149
+          <t>-402,068
 Cr. -40.21</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>23.10</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3019,19 +3019,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>92,648
-Cr. 9.26</t>
+          <t>94,918
+Cr. 9.49</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-215,195
-Cr. -21.52</t>
+          <t>-212,925
+Cr. -21.29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.10</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3179,19 +3179,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>42,044
-Cr. 4.20</t>
+          <t>52,019
+Cr. 5.20</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-55,456
-Cr. -5.55</t>
+          <t>-45,481
+Cr. -4.55</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3219,19 +3219,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>117,954
-Cr. 11.80</t>
+          <t>125,269
+Cr. 12.53</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-192,958
-Cr. -19.30</t>
+          <t>-185,643
+Cr. -18.56</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3299,19 +3299,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>85,279
-Cr. 8.53</t>
+          <t>98,749
+Cr. 9.87</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-230,454
-Cr. -23.05</t>
+          <t>-216,984
+Cr. -21.70</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>31.28</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3411,19 +3411,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,155,709
-Cr. 415.57</t>
+          <t>4,250,558
+Cr. 425.06</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-1,451,992
-Cr. -145.20</t>
+          <t>-1,357,143
+Cr. -135.71</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>75.80</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 17.08.2026</t>
+          <t>Open Line FR Fund Wise - As On 27.08.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3544,24 +3544,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>354,585
-Cr. 35.46</t>
+          <t>380,485
+Cr. 38.05</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>663,768
-Cr. 66.38</t>
+          <t>637,868
+Cr. 63.79</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>65.18</t>
+          <t>62.64</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3704,24 +3704,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,142,858
-Cr. 314.29</t>
+          <t>3,175,144
+Cr. 317.51</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-25,343
-Cr. -2.53</t>
+          <t>-57,629
+Cr. -5.76</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>100.81</t>
+          <t>101.85</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3784,24 +3784,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>631,485
-Cr. 63.15</t>
+          <t>668,148
+Cr. 66.81</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>669,524
-Cr. 66.95</t>
+          <t>632,861
+Cr. 63.29</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -630,30 +630,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>232,594
-Cr. 23.26</t>
+          <t>236,563
+Cr. 23.66</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>-7,437
-Cr. -0.74</t>
+          <t>-3,468
+Cr. -0.35</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>408,928
-Cr. 40.89</t>
+          <t>404,959
+Cr. 40.50</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -688,14 +688,14 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,467,818
-Cr. 146.78</t>
+          <t>1,473,830
+Cr. 147.38</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>289,834
-Cr. 28.98</t>
+          <t>295,846
+Cr. 29.58</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -705,8 +705,8 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>2,141,084
-Cr. 214.11</t>
+          <t>2,135,072
+Cr. 213.51</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -804,30 +804,30 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>722,606
-Cr. 72.26</t>
+          <t>765,059
+Cr. 76.51</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>308,646
-Cr. 30.86</t>
+          <t>351,099
+Cr. 35.11</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>630,975
-Cr. 63.10</t>
+          <t>588,522
+Cr. 58.85</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -862,30 +862,30 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>800,112
-Cr. 80.01</t>
+          <t>838,163
+Cr. 83.82</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105,972
-Cr. 10.60</t>
+          <t>144,023
+Cr. 14.40</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,259,838
-Cr. 125.98</t>
+          <t>1,221,787
+Cr. 122.18</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -920,30 +920,30 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,562,963
-Cr. 156.30</t>
+          <t>1,617,389
+Cr. 161.74</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>345,691
-Cr. 34.57</t>
+          <t>400,117
+Cr. 40.01</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,789,603
-Cr. 178.96</t>
+          <t>1,735,177
+Cr. 173.52</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1,777,301
-Cr. 177.73</t>
+          <t>1,782,151
+Cr. 178.22</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>266,110
-Cr. 26.61</t>
+          <t>270,960
+Cr. 27.10</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -995,8 +995,8 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,651,465
-Cr. 265.15</t>
+          <t>2,646,615
+Cr. 264.66</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1036,30 +1036,30 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3,545,214
-Cr. 354.52</t>
+          <t>4,605,644
+Cr. 460.56</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>-317,091
-Cr. -31.71</t>
+          <t>743,339
+Cr. 74.33</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8,061,992
-Cr. 806.20</t>
+          <t>7,001,562
+Cr. 700.16</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>807,750
-Cr. 80.78</t>
+          <t>810,746
+Cr. 81.07</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>209,076
-Cr. 20.91</t>
+          <t>212,072
+Cr. 21.21</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1111,8 +1111,8 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>585,082
-Cr. 58.51</t>
+          <t>582,086
+Cr. 58.21</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1152,25 +1152,25 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>355,866
-Cr. 35.59</t>
+          <t>356,768
+Cr. 35.68</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>30,178
-Cr. 3.02</t>
+          <t>31,080
+Cr. 3.11</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>638,772
-Cr. 63.88</t>
+          <t>637,870
+Cr. 63.79</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1264,30 +1264,30 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>12,479,934
-Cr. 1247.99</t>
+          <t>13,694,023
+Cr. 1369.40</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1,126,378
-Cr. 112.64</t>
+          <t>2,340,467
+Cr. 234.05</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>20,115,939
-Cr. 2011.59</t>
+          <t>18,901,850
+Cr. 1890.18</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1322,14 +1322,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,569,032
-Cr. 156.90</t>
+          <t>1,569,443
+Cr. 156.94</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>206,233
-Cr. 20.62</t>
+          <t>206,644
+Cr. 20.66</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1339,13 +1339,13 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,582,077
-Cr. -158.21</t>
+          <t>-1,582,488
+Cr. -158.25</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12028</t>
+          <t>-12031</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>PU Wise - Staff - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1505,14 +1505,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2,454,892
-Cr. 245.49</t>
+          <t>2,453,873
+Cr. 245.39</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>205,828
-Cr. 20.58</t>
+          <t>204,809
+Cr. 20.48</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1522,8 +1522,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4,251,517
-Cr. 425.15</t>
+          <t>4,252,536
+Cr. 425.25</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,579,845
-Cr. 157.98</t>
+          <t>1,579,536
+Cr. 157.95</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>220,441
-Cr. 22.04</t>
+          <t>220,132
+Cr. 22.01</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1575,8 +1575,8 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,520,608
-Cr. 252.06</t>
+          <t>2,520,917
+Cr. 252.09</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>269,991
-Cr. 27.00</t>
+          <t>269,887
+Cr. 26.99</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1,139
-Cr. 0.11</t>
+          <t>1,035
+Cr. 0.10</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1681,8 +1681,8 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>506,207
-Cr. 50.62</t>
+          <t>506,311
+Cr. 50.63</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1717,13 +1717,13 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>173,507
+          <t>173,467
 Cr. 17.35</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6,195
+          <t>6,155
 Cr. 0.62</t>
         </is>
       </c>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>323,102
+          <t>323,142
 Cr. 32.31</t>
         </is>
       </c>
@@ -1823,14 +1823,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>54,545
-Cr. 5.45</t>
+          <t>54,782
+Cr. 5.48</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>27,621
-Cr. 2.76</t>
+          <t>27,858
+Cr. 2.79</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1840,8 +1840,8 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>22,755
-Cr. 2.28</t>
+          <t>22,518
+Cr. 2.25</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1929,13 +1929,13 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>250,793
-Cr. 25.08</t>
+          <t>250,736
+Cr. 25.07</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>-22,684
+          <t>-22,741
 Cr. -2.27</t>
         </is>
       </c>
@@ -1946,8 +1946,8 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>277,039
-Cr. 27.70</t>
+          <t>277,096
+Cr. 27.71</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5,715,910
-Cr. 571.59</t>
+          <t>5,714,618
+Cr. 571.46</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>619,931
-Cr. 61.99</t>
+          <t>618,639
+Cr. 61.86</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2158,8 +2158,8 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>8,847,637
-Cr. 884.76</t>
+          <t>8,848,929
+Cr. 884.89</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2193,7 +2193,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -2203,7 +2203,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2324,30 +2324,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>588,317
-Cr. 58.83</t>
+          <t>737,391
+Cr. 73.74</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>237,595
-Cr. 23.76</t>
+          <t>386,669
+Cr. 38.67</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>480,435
-Cr. 48.04</t>
+          <t>331,361
+Cr. 33.14</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2377,14 +2377,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>63,019
-Cr. 6.30</t>
+          <t>63,087
+Cr. 6.31</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>10,300
-Cr. 1.03</t>
+          <t>10,368
+Cr. 1.04</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>86,928
+          <t>86,860
 Cr. 8.69</t>
         </is>
       </c>
@@ -2430,30 +2430,30 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,100,220
-Cr. 110.02</t>
+          <t>1,415,221
+Cr. 141.52</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-230,054
-Cr. -23.01</t>
+          <t>84,947
+Cr. 8.49</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2,778,504
-Cr. 277.85</t>
+          <t>2,463,503
+Cr. 246.35</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -2483,30 +2483,30 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1,658,467
-Cr. 165.85</t>
+          <t>1,686,250
+Cr. 168.62</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>262,139
-Cr. 26.21</t>
+          <t>289,922
+Cr. 28.99</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1,595,843
-Cr. 159.58</t>
+          <t>1,568,060
+Cr. 156.81</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2536,30 +2536,30 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1,807,074
-Cr. 180.71</t>
+          <t>2,303,206
+Cr. 230.32</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>268,642
-Cr. 26.86</t>
+          <t>764,774
+Cr. 76.48</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2,896,282
-Cr. 289.63</t>
+          <t>2,400,150
+Cr. 240.01</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -2589,30 +2589,30 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>5,217,097
-Cr. 521.71</t>
+          <t>6,205,155
+Cr. 620.52</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>548,622
-Cr. 54.86</t>
+          <t>1,536,680
+Cr. 153.67</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>7,837,992
-Cr. 783.80</t>
+          <t>6,849,934
+Cr. 684.99</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - JUL 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - JUL 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - JU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 27." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -559,14 +559,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUL 2026</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUL 2026</t>
+Actuals up to AUG 2026</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -624,36 +624,36 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>240,031
-Cr. 24.00</t>
+          <t>267,301
+Cr. 26.73</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>236,563
-Cr. 23.66</t>
+          <t>294,025
+Cr. 29.40</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>-3,468
-Cr. -0.35</t>
+          <t>26,724
+Cr. 2.67</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>404,959
-Cr. 40.50</t>
+          <t>347,497
+Cr. 34.75</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -682,36 +682,36 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,177,984
-Cr. 117.80</t>
+          <t>1,503,709
+Cr. 150.37</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,473,830
-Cr. 147.38</t>
+          <t>1,779,391
+Cr. 177.94</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>295,846
-Cr. 29.58</t>
+          <t>275,682
+Cr. 27.57</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>2,135,072
-Cr. 213.51</t>
+          <t>1,829,511
+Cr. 182.95</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -740,8 +740,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>923,741
-Cr. 92.37</t>
+          <t>777,018
+Cr. 77.70</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -752,13 +752,13 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>-141,709
-Cr. -14.17</t>
+          <t>5,014
+Cr. 0.50</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -798,36 +798,36 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>413,960
-Cr. 41.40</t>
+          <t>563,992
+Cr. 56.40</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>765,059
-Cr. 76.51</t>
+          <t>882,060
+Cr. 88.21</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>351,099
-Cr. 35.11</t>
+          <t>318,068
+Cr. 31.81</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>588,522
-Cr. 58.85</t>
+          <t>471,521
+Cr. 47.15</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -856,36 +856,36 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>694,140
-Cr. 69.41</t>
+          <t>858,312
+Cr. 85.83</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>838,163
-Cr. 83.82</t>
+          <t>987,240
+Cr. 98.72</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>144,023
-Cr. 14.40</t>
+          <t>128,928
+Cr. 12.89</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,221,787
-Cr. 122.18</t>
+          <t>1,072,710
+Cr. 107.27</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -914,36 +914,36 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1,217,272
-Cr. 121.73</t>
+          <t>1,396,902
+Cr. 139.69</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,617,389
-Cr. 161.74</t>
+          <t>1,953,133
+Cr. 195.31</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>400,117
-Cr. 40.01</t>
+          <t>556,231
+Cr. 55.62</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,735,177
-Cr. 173.52</t>
+          <t>1,399,433
+Cr. 139.94</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -972,36 +972,36 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,511,191
-Cr. 151.12</t>
+          <t>1,845,319
+Cr. 184.53</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1,782,151
-Cr. 178.22</t>
+          <t>2,193,589
+Cr. 219.36</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>270,960
-Cr. 27.10</t>
+          <t>348,270
+Cr. 34.83</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,646,615
-Cr. 264.66</t>
+          <t>2,235,177
+Cr. 223.52</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1030,31 +1030,31 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>3,862,305
-Cr. 386.23</t>
+          <t>4,836,336
+Cr. 483.63</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4,605,644
-Cr. 460.56</t>
+          <t>4,657,805
+Cr. 465.78</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>743,339
-Cr. 74.33</t>
+          <t>-178,531
+Cr. -17.85</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>7,001,562
-Cr. 700.16</t>
+          <t>6,949,401
+Cr. 694.94</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1088,36 +1088,36 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>598,674
-Cr. 59.87</t>
+          <t>580,347
+Cr. 58.03</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>810,746
-Cr. 81.07</t>
+          <t>915,762
+Cr. 91.58</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>212,072
-Cr. 21.21</t>
+          <t>335,415
+Cr. 33.54</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>582,086
-Cr. 58.21</t>
+          <t>477,070
+Cr. 47.71</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1146,36 +1146,36 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>325,688
-Cr. 32.57</t>
+          <t>414,432
+Cr. 41.44</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>356,768
-Cr. 35.68</t>
+          <t>439,544
+Cr. 43.95</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>31,080
-Cr. 3.11</t>
+          <t>25,112
+Cr. 2.51</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>637,870
-Cr. 63.79</t>
+          <t>555,094
+Cr. 55.51</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1204,36 +1204,36 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>388,570
-Cr. 38.86</t>
+          <t>537,945
+Cr. 53.79</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>425,678
-Cr. 42.57</t>
+          <t>532,662
+Cr. 53.27</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>37,108
-Cr. 3.71</t>
+          <t>-5,283
+Cr. -0.53</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>865,389
-Cr. 86.54</t>
+          <t>758,405
+Cr. 75.84</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1258,36 +1258,36 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>11,353,556
-Cr. 1135.36</t>
+          <t>13,581,613
+Cr. 1358.16</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>13,694,023
-Cr. 1369.40</t>
+          <t>15,417,243
+Cr. 1541.72</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2,340,467
-Cr. 234.05</t>
+          <t>1,835,630
+Cr. 183.56</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>18,901,850
-Cr. 1890.18</t>
+          <t>17,178,630
+Cr. 1717.86</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1316,36 +1316,36 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1,362,799
-Cr. 136.28</t>
+          <t>-5,435
+Cr. -0.54</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,569,443
-Cr. 156.94</t>
+          <t>1,578,852
+Cr. 157.89</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>206,644
-Cr. 20.66</t>
+          <t>1,584,287
+Cr. 158.43</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>-29050</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,582,488
-Cr. -158.25</t>
+          <t>-1,591,897
+Cr. -159.19</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12031</t>
+          <t>-12103</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -1384,7 +1384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1439,14 +1439,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUL 2026</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUL 2026</t>
+Actuals up to AUG 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1499,36 +1499,36 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,249,064
-Cr. 224.91</t>
+          <t>2,794,337
+Cr. 279.43</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2,453,873
-Cr. 245.39</t>
+          <t>3,073,272
+Cr. 307.33</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>204,809
-Cr. 20.48</t>
+          <t>278,935
+Cr. 27.89</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4,252,536
-Cr. 425.25</t>
+          <t>3,633,137
+Cr. 363.31</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1552,36 +1552,36 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,359,404
-Cr. 135.94</t>
+          <t>1,708,522
+Cr. 170.85</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,579,536
-Cr. 157.95</t>
+          <t>1,968,578
+Cr. 196.86</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>220,132
-Cr. 22.01</t>
+          <t>260,056
+Cr. 26.01</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,520,917
-Cr. 252.09</t>
+          <t>2,131,875
+Cr. 213.19</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1605,8 +1605,8 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>118,787
+Cr. 11.88</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1617,8 +1617,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>81
-Cr. 0.01</t>
+          <t>-118,706
+Cr. -11.87</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1658,36 +1658,36 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>268,852
-Cr. 26.89</t>
+          <t>323,416
+Cr. 32.34</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>269,887
-Cr. 26.99</t>
+          <t>337,922
+Cr. 33.79</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1,035
-Cr. 0.10</t>
+          <t>14,506
+Cr. 1.45</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>506,311
-Cr. 50.63</t>
+          <t>438,276
+Cr. 43.83</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1711,36 +1711,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>167,312
-Cr. 16.73</t>
+          <t>206,920
+Cr. 20.69</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>173,467
-Cr. 17.35</t>
+          <t>216,618
+Cr. 21.66</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6,155
-Cr. 0.62</t>
+          <t>9,698
+Cr. 0.97</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>323,142
-Cr. 32.31</t>
+          <t>279,991
+Cr. 28.00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1764,36 +1764,36 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>255,207
-Cr. 25.52</t>
+          <t>283,415
+Cr. 28.34</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>290,482
-Cr. 29.05</t>
+          <t>364,653
+Cr. 36.47</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>35,275
-Cr. 3.53</t>
+          <t>81,238
+Cr. 8.12</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>389,715
-Cr. 38.97</t>
+          <t>315,544
+Cr. 31.55</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1817,36 +1817,36 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>26,924
-Cr. 2.69</t>
+          <t>32,208
+Cr. 3.22</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>54,782
-Cr. 5.48</t>
+          <t>59,582
+Cr. 5.96</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>27,858
-Cr. 2.79</t>
+          <t>27,374
+Cr. 2.74</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>22,518
-Cr. 2.25</t>
+          <t>17,718
+Cr. 1.77</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1870,36 +1870,36 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>69,543
-Cr. 6.95</t>
+          <t>87,464
+Cr. 8.75</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>98,022
-Cr. 9.80</t>
+          <t>122,506
+Cr. 12.25</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>28,479
-Cr. 2.85</t>
+          <t>35,042
+Cr. 3.50</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>111,891
-Cr. 11.19</t>
+          <t>87,407
+Cr. 8.74</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1923,36 +1923,36 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>273,477
-Cr. 27.35</t>
+          <t>219,930
+Cr. 21.99</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>250,736
-Cr. 25.07</t>
+          <t>279,175
+Cr. 27.92</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>-22,741
-Cr. -2.27</t>
+          <t>59,245
+Cr. 5.92</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>277,096
-Cr. 27.71</t>
+          <t>248,657
+Cr. 24.87</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1976,36 +1976,36 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>5,665
-Cr. 0.57</t>
+          <t>6,687
+Cr. 0.67</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>9,177
-Cr. 0.92</t>
+          <t>11,132
+Cr. 1.11</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>3,512
-Cr. 0.35</t>
+          <t>4,445
+Cr. 0.44</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>6,871
-Cr. 0.69</t>
+          <t>4,916
+Cr. 0.49</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2029,36 +2029,36 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>100,083
-Cr. 10.01</t>
+          <t>128,367
+Cr. 12.84</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>176,120
-Cr. 17.61</t>
+          <t>217,182
+Cr. 21.72</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>76,037
-Cr. 7.60</t>
+          <t>88,815
+Cr. 8.88</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>131,961
-Cr. 13.20</t>
+          <t>90,899
+Cr. 9.09</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -2082,36 +2082,36 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>320,448
-Cr. 32.04</t>
+          <t>158,091
+Cr. 15.81</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>358,455
-Cr. 35.85</t>
+          <t>374,892
+Cr. 37.49</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>38,007
-Cr. 3.80</t>
+          <t>216,801
+Cr. 21.68</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>20,963
-Cr. 2.10</t>
+          <t>4,526
+Cr. 0.45</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2135,36 +2135,36 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>5,095,979
-Cr. 509.60</t>
+          <t>6,068,144
+Cr. 606.81</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5,714,618
-Cr. 571.46</t>
+          <t>7,025,593
+Cr. 702.56</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>618,639
-Cr. 61.86</t>
+          <t>957,449
+Cr. 95.74</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>8,848,929
-Cr. 884.89</t>
+          <t>7,537,954
+Cr. 753.80</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2258,14 +2258,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUL 2026</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUL 2026</t>
+Actuals up to AUG 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2318,36 +2318,36 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>350,722
-Cr. 35.07</t>
+          <t>445,313
+Cr. 44.53</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>737,391
-Cr. 73.74</t>
+          <t>746,612
+Cr. 74.66</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>386,669
-Cr. 38.67</t>
+          <t>301,299
+Cr. 30.13</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>331,361
-Cr. 33.14</t>
+          <t>322,140
+Cr. 32.21</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2371,36 +2371,36 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>52,719
-Cr. 5.27</t>
+          <t>62,478
+Cr. 6.25</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>63,087
-Cr. 6.31</t>
+          <t>70,596
+Cr. 7.06</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>10,368
-Cr. 1.04</t>
+          <t>8,118
+Cr. 0.81</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>86,860
-Cr. 8.69</t>
+          <t>79,351
+Cr. 7.94</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -2424,36 +2424,36 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1,330,274
-Cr. 133.03</t>
+          <t>1,616,135
+Cr. 161.61</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,415,221
-Cr. 141.52</t>
+          <t>1,504,722
+Cr. 150.47</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>84,947
-Cr. 8.49</t>
+          <t>-111,413
+Cr. -11.14</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2,463,503
-Cr. 246.35</t>
+          <t>2,374,002
+Cr. 237.40</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -2477,36 +2477,36 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1,396,328
-Cr. 139.63</t>
+          <t>1,355,962
+Cr. 135.60</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1,686,250
-Cr. 168.62</t>
+          <t>1,822,493
+Cr. 182.25</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>289,922
-Cr. 28.99</t>
+          <t>466,531
+Cr. 46.65</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>134</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1,568,060
-Cr. 156.81</t>
+          <t>1,431,817
+Cr. 143.18</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2530,8 +2530,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1,538,432
-Cr. 153.84</t>
+          <t>1,959,732
+Cr. 195.97</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2542,13 +2542,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>764,774
-Cr. 76.48</t>
+          <t>343,474
+Cr. 34.35</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2583,36 +2583,36 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4,668,475
-Cr. 466.85</t>
+          <t>5,439,620
+Cr. 543.96</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>6,205,155
-Cr. 620.52</t>
+          <t>6,447,629
+Cr. 644.76</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,536,680
-Cr. 153.67</t>
+          <t>1,008,009
+Cr. 100.80</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>6,849,934
-Cr. 684.99</t>
+          <t>6,607,460
+Cr. 660.75</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1384,7 +1384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2203,7 +2203,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1384,7 +1384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2203,7 +2203,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
+++ b/exports/Moradabad_Division_DRM_Budget_FR_Analysis.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Staff - AUG 2026 | up" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Wise - Non-Staff Part 1 - AU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 27." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -496,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -630,14 +630,14 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>294,025
-Cr. 29.40</t>
+          <t>294,135
+Cr. 29.41</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26,724
-Cr. 2.67</t>
+          <t>26,834
+Cr. 2.68</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -647,8 +647,8 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>347,497
-Cr. 34.75</t>
+          <t>347,387
+Cr. 34.74</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -688,14 +688,14 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,779,391
-Cr. 177.94</t>
+          <t>1,781,320
+Cr. 178.13</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>275,682
-Cr. 27.57</t>
+          <t>277,611
+Cr. 27.76</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -705,8 +705,8 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1,829,511
-Cr. 182.95</t>
+          <t>1,827,582
+Cr. 182.76</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -804,30 +804,30 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>882,060
-Cr. 88.21</t>
+          <t>911,131
+Cr. 91.11</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>318,068
-Cr. 31.81</t>
+          <t>347,139
+Cr. 34.71</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>471,521
-Cr. 47.15</t>
+          <t>442,450
+Cr. 44.24</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -862,25 +862,25 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>987,240
-Cr. 98.72</t>
+          <t>995,022
+Cr. 99.50</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>128,928
-Cr. 12.89</t>
+          <t>136,710
+Cr. 13.67</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,072,710
-Cr. 107.27</t>
+          <t>1,064,928
+Cr. 106.49</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -920,30 +920,30 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,953,133
-Cr. 195.31</t>
+          <t>1,978,638
+Cr. 197.86</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>556,231
-Cr. 55.62</t>
+          <t>581,736
+Cr. 58.17</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,399,433
-Cr. 139.94</t>
+          <t>1,373,928
+Cr. 137.39</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2,193,589
-Cr. 219.36</t>
+          <t>2,192,865
+Cr. 219.29</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>348,270
-Cr. 34.83</t>
+          <t>347,546
+Cr. 34.75</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -995,8 +995,8 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,235,177
-Cr. 223.52</t>
+          <t>2,235,901
+Cr. 223.59</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1036,30 +1036,30 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4,657,805
-Cr. 465.78</t>
+          <t>5,702,475
+Cr. 570.25</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>-178,531
-Cr. -17.85</t>
+          <t>866,139
+Cr. 86.61</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>6,949,401
-Cr. 694.94</t>
+          <t>5,904,731
+Cr. 590.47</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>915,762
-Cr. 91.58</t>
+          <t>916,954
+Cr. 91.70</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>335,415
-Cr. 33.54</t>
+          <t>336,607
+Cr. 33.66</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1111,8 +1111,8 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>477,070
-Cr. 47.71</t>
+          <t>475,878
+Cr. 47.59</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1152,25 +1152,25 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>439,544
-Cr. 43.95</t>
+          <t>441,761
+Cr. 44.18</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>25,112
-Cr. 2.51</t>
+          <t>27,328
+Cr. 2.73</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>555,094
-Cr. 55.51</t>
+          <t>552,877
+Cr. 55.29</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1258,36 +1258,36 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>13,581,613
+          <t>13,581,614
 Cr. 1358.16</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>15,417,243
-Cr. 1541.72</t>
+          <t>16,528,995
+Cr. 1652.90</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1,835,630
-Cr. 183.56</t>
+          <t>2,947,381
+Cr. 294.74</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>17,178,630
-Cr. 1717.86</t>
+          <t>16,066,878
+Cr. 1606.69</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1322,30 +1322,30 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,578,852
-Cr. 157.89</t>
+          <t>1,578,052
+Cr. 157.81</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1,584,287
-Cr. 158.43</t>
+          <t>1,583,487
+Cr. 158.35</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-29050</t>
+          <t>-29033</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,591,897
-Cr. -159.19</t>
+          <t>-1,591,097
+Cr. -159.11</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12103</t>
+          <t>-12097</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>PU Wise - Staff - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1505,14 +1505,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3,073,272
-Cr. 307.33</t>
+          <t>3,071,823
+Cr. 307.18</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>278,935
-Cr. 27.89</t>
+          <t>277,486
+Cr. 27.75</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1522,8 +1522,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>3,633,137
-Cr. 363.31</t>
+          <t>3,634,586
+Cr. 363.46</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,968,578
-Cr. 196.86</t>
+          <t>1,966,618
+Cr. 196.66</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>260,056
-Cr. 26.01</t>
+          <t>258,096
+Cr. 25.81</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1575,8 +1575,8 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,131,875
-Cr. 213.19</t>
+          <t>2,133,835
+Cr. 213.38</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1611,13 +1611,13 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>81
+          <t>72
 Cr. 0.01</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-118,706
+          <t>-118,715
 Cr. -11.87</t>
         </is>
       </c>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>285,008
+          <t>285,017
 Cr. 28.50</t>
         </is>
       </c>
@@ -1664,14 +1664,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>337,922
-Cr. 33.79</t>
+          <t>337,362
+Cr. 33.74</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>14,506
-Cr. 1.45</t>
+          <t>13,946
+Cr. 1.39</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1681,13 +1681,13 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>438,276
-Cr. 43.83</t>
+          <t>438,836
+Cr. 43.88</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>216,618
-Cr. 21.66</t>
+          <t>216,397
+Cr. 21.64</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>9,698
-Cr. 0.97</t>
+          <t>9,477
+Cr. 0.95</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1734,8 +1734,8 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>279,991
-Cr. 28.00</t>
+          <t>280,212
+Cr. 28.02</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1876,13 +1876,13 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>122,506
+          <t>122,492
 Cr. 12.25</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>35,042
+          <t>35,028
 Cr. 3.50</t>
         </is>
       </c>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>87,407
+          <t>87,421
 Cr. 8.74</t>
         </is>
       </c>
@@ -1929,14 +1929,14 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>279,175
-Cr. 27.92</t>
+          <t>278,899
+Cr. 27.89</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>59,245
-Cr. 5.92</t>
+          <t>58,969
+Cr. 5.90</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1946,8 +1946,8 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>248,657
-Cr. 24.87</t>
+          <t>248,933
+Cr. 24.89</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2035,14 +2035,14 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>217,182
-Cr. 21.72</t>
+          <t>217,100
+Cr. 21.71</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>88,815
-Cr. 8.88</t>
+          <t>88,733
+Cr. 8.87</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -2052,8 +2052,8 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>90,899
-Cr. 9.09</t>
+          <t>90,981
+Cr. 9.10</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -2088,14 +2088,14 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>374,892
-Cr. 37.49</t>
+          <t>375,011
+Cr. 37.50</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>216,801
-Cr. 21.68</t>
+          <t>216,920
+Cr. 21.69</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2105,8 +2105,8 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>4,526
-Cr. 0.45</t>
+          <t>4,407
+Cr. 0.44</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2135,20 +2135,20 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>6,068,144
+          <t>6,068,145
 Cr. 606.81</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7,025,593
-Cr. 702.56</t>
+          <t>7,021,141
+Cr. 702.11</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>957,449
-Cr. 95.74</t>
+          <t>952,996
+Cr. 95.30</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2158,8 +2158,8 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>7,537,954
-Cr. 753.80</t>
+          <t>7,542,406
+Cr. 754.24</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>PU Wise - Non-Staff Part 1 - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2324,30 +2324,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>746,612
-Cr. 74.66</t>
+          <t>860,139
+Cr. 86.01</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>301,299
-Cr. 30.13</t>
+          <t>414,826
+Cr. 41.48</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>322,140
-Cr. 32.21</t>
+          <t>208,613
+Cr. 20.86</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -2377,13 +2377,13 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>70,596
+          <t>70,608
 Cr. 7.06</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>8,118
+          <t>8,130
 Cr. 0.81</t>
         </is>
       </c>
@@ -2394,8 +2394,8 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>79,351
-Cr. 7.94</t>
+          <t>79,339
+Cr. 7.93</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -2430,30 +2430,30 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1,504,722
-Cr. 150.47</t>
+          <t>1,916,509
+Cr. 191.65</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-111,413
-Cr. -11.14</t>
+          <t>300,374
+Cr. 30.04</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2,374,002
-Cr. 237.40</t>
+          <t>1,962,215
+Cr. 196.22</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -2483,25 +2483,25 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1,822,493
-Cr. 182.25</t>
+          <t>1,824,117
+Cr. 182.41</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>466,531
-Cr. 46.65</t>
+          <t>468,154
+Cr. 46.82</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1,431,817
-Cr. 143.18</t>
+          <t>1,430,193
+Cr. 143.02</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -2536,30 +2536,30 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2,303,206
-Cr. 230.32</t>
+          <t>2,715,415
+Cr. 271.54</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>343,474
-Cr. 34.35</t>
+          <t>755,683
+Cr. 75.57</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2,400,150
-Cr. 240.01</t>
+          <t>1,987,941
+Cr. 198.79</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -2589,30 +2589,30 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>6,447,629
-Cr. 644.76</t>
+          <t>7,386,788
+Cr. 738.68</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,008,009
-Cr. 100.80</t>
+          <t>1,947,168
+Cr. 194.72</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>6,607,460
-Cr. 660.75</t>
+          <t>5,668,301
+Cr. 566.83</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 27.08.2026</t>
+          <t>Open Line FR Report - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2739,19 +2739,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,175
-Cr. 7.72</t>
+          <t>77,992
+Cr. 7.80</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-83,728
-Cr. -8.37</t>
+          <t>-82,911
+Cr. -8.29</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2779,19 +2779,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>10,761
-Cr. 1.08</t>
+          <t>11,801
+Cr. 1.18</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-21,466
-Cr. -2.15</t>
+          <t>-20,426
+Cr. -2.04</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57,023
-Cr. 5.70</t>
+          <t>57,289
+Cr. 5.73</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-63,295
-Cr. -6.33</t>
+          <t>-63,029
+Cr. -6.30</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2859,19 +2859,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>337,625
-Cr. 33.76</t>
+          <t>363,937
+Cr. 36.39</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-169,795
-Cr. -16.98</t>
+          <t>-143,483
+Cr. -14.35</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>71.72</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2899,19 +2899,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,110,796
-Cr. 311.08</t>
+          <t>3,692,699
+Cr. 369.27</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>148,001
-Cr. 14.80</t>
+          <t>729,904
+Cr. 72.99</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105.00</t>
+          <t>124.64</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>150,620
-Cr. 15.06</t>
+          <t>151,197
+Cr. 15.12</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18,353
-Cr. 1.84</t>
+          <t>18,930
+Cr. 1.89</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>113.88</t>
+          <t>114.31</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2979,19 +2979,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>120,775
-Cr. 12.08</t>
+          <t>123,038
+Cr. 12.30</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-402,068
-Cr. -40.21</t>
+          <t>-399,805
+Cr. -39.98</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.10</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3019,19 +3019,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>94,918
+          <t>94,924
 Cr. 9.49</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-212,925
+          <t>-212,919
 Cr. -21.29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3099,19 +3099,19 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>10,501
-Cr. 1.05</t>
+          <t>24,273
+Cr. 2.43</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-2,693
-Cr. -0.27</t>
+          <t>11,079
+Cr. 1.11</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>79.59</t>
+          <t>183.97</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -3139,19 +3139,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4,327
-Cr. 0.43</t>
+          <t>5,129
+Cr. 0.51</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-49,375
-Cr. -4.94</t>
+          <t>-48,573
+Cr. -4.86</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3179,19 +3179,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>52,019
-Cr. 5.20</t>
+          <t>59,852
+Cr. 5.99</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-45,481
-Cr. -4.55</t>
+          <t>-37,648
+Cr. -3.76</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>61.39</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3219,19 +3219,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>125,269
-Cr. 12.53</t>
+          <t>131,048
+Cr. 13.10</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-185,643
-Cr. -18.56</t>
+          <t>-179,864
+Cr. -17.99</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3299,19 +3299,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>98,749
-Cr. 9.87</t>
+          <t>103,375
+Cr. 10.34</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-216,984
-Cr. -21.70</t>
+          <t>-212,358
+Cr. -21.24</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3411,19 +3411,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,250,558
-Cr. 425.06</t>
+          <t>4,896,554
+Cr. 489.66</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-1,357,143
-Cr. -135.71</t>
+          <t>-711,147
+Cr. -71.11</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>75.80</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 27.08.2026</t>
+          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3544,24 +3544,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>380,485
-Cr. 38.05</t>
+          <t>408,842
+Cr. 40.88</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>637,868
-Cr. 63.79</t>
+          <t>609,511
+Cr. 60.95</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>62.64</t>
+          <t>59.85</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3624,24 +3624,24 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>11,290
-Cr. 1.13</t>
+          <t>18,459
+Cr. 1.85</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>119,302
-Cr. 11.93</t>
+          <t>112,133
+Cr. 11.21</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>91.35</t>
+          <t>85.87</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3704,24 +3704,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,175,144
-Cr. 317.51</t>
+          <t>3,746,106
+Cr. 374.61</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-57,629
-Cr. -5.76</t>
+          <t>-628,591
+Cr. -62.86</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>101.85</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-20.16</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3784,24 +3784,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>668,148
-Cr. 66.81</t>
+          <t>707,656
+Cr. 70.77</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>632,861
-Cr. 63.29</t>
+          <t>593,353
+Cr. 59.34</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>45.61</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
